--- a/public/modelos/Contas_a_Receber.xlsx
+++ b/public/modelos/Contas_a_Receber.xlsx
@@ -397,16 +397,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
     <col min="3" max="3" width="15.83203125" customWidth="1"/>
     <col min="4" max="4" width="15.83203125" customWidth="1"/>
-    <col min="5" max="5" width="22.83203125" customWidth="1"/>
+    <col min="5" max="5" width="20.83203125" customWidth="1"/>
     <col min="6" max="6" width="22.83203125" customWidth="1"/>
-    <col min="7" max="7" width="28.83203125" customWidth="1"/>
-    <col min="8" max="8" width="15.83203125" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1"/>
+    <col min="8" max="8" width="28.83203125" customWidth="1"/>
+    <col min="9" max="9" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -423,15 +424,18 @@
         <v>Vencimento</v>
       </c>
       <c r="E1" t="str">
+        <v>Data de Pagamento</v>
+      </c>
+      <c r="F1" t="str">
         <v>Forma de Pagamento</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Caixa / Origem</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Cliente</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>Status</v>
       </c>
     </row>
@@ -440,7 +444,7 @@
         <v>Consultoria Técnica</v>
       </c>
       <c r="B2" t="str">
-        <v>Serviços</v>
+        <v>Prestação de Serviços</v>
       </c>
       <c r="C2">
         <v>1500</v>
@@ -449,16 +453,19 @@
         <v>20/10/2026</v>
       </c>
       <c r="E2" t="str">
+        <v>20/10/2026</v>
+      </c>
+      <c r="F2" t="str">
         <v>Pix</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>Caixa Principal</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v>Empresa Exemplo LTDA</v>
       </c>
-      <c r="H2" t="str">
-        <v>Pendente</v>
+      <c r="I2" t="str">
+        <v>Recebido</v>
       </c>
     </row>
     <row r="3">
@@ -475,15 +482,18 @@
         <v>25/10/2026</v>
       </c>
       <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
         <v>Boleto</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
         <v>Conta Bancária</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v/>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
         <v>Pendente</v>
       </c>
     </row>
@@ -492,7 +502,7 @@
         <v>Manutenção Preventiva</v>
       </c>
       <c r="B4" t="str">
-        <v>Serviços</v>
+        <v>Prestação de Serviços</v>
       </c>
       <c r="C4">
         <v>420</v>
@@ -501,21 +511,24 @@
         <v>15/10/2026</v>
       </c>
       <c r="E4" t="str">
+        <v>14/10/2026</v>
+      </c>
+      <c r="F4" t="str">
         <v>Cartão de Crédito</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
         <v>Caixa Principal</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>João da Silva</v>
       </c>
-      <c r="H4" t="str">
+      <c r="I4" t="str">
         <v>Recebido</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/modelos/Contas_a_Receber.xlsx
+++ b/public/modelos/Contas_a_Receber.xlsx
@@ -4,6 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Contas a Receber" sheetId="1" r:id="rId1"/>
+    <sheet name="Orientações" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -397,17 +398,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:L6"/>
   <cols>
-    <col min="1" max="1" width="30.83203125" customWidth="1"/>
-    <col min="2" max="2" width="22.83203125" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
+    <col min="1" max="1" width="38.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" customWidth="1"/>
     <col min="6" max="6" width="22.83203125" customWidth="1"/>
     <col min="7" max="7" width="20.83203125" customWidth="1"/>
-    <col min="8" max="8" width="28.83203125" customWidth="1"/>
-    <col min="9" max="9" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="32.83203125" customWidth="1"/>
+    <col min="9" max="9" width="22.83203125" customWidth="1"/>
+    <col min="10" max="10" width="24.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="12" max="12" width="35.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -436,18 +440,27 @@
         <v>Cliente</v>
       </c>
       <c r="I1" t="str">
+        <v>CPF / CNPJ</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Ordem de Serviço (O.S.)</v>
+      </c>
+      <c r="K1" t="str">
         <v>Status</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Observações</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Consultoria Técnica</v>
+        <v>Consultoria Técnica Especializada</v>
       </c>
       <c r="B2" t="str">
         <v>Prestação de Serviços</v>
       </c>
-      <c r="C2">
-        <v>1500</v>
+      <c r="C2" t="str">
+        <v>1500,00</v>
       </c>
       <c r="D2" t="str">
         <v>20/10/2026</v>
@@ -465,18 +478,27 @@
         <v>Empresa Exemplo LTDA</v>
       </c>
       <c r="I2" t="str">
+        <v>12.345.678/0001-90</v>
+      </c>
+      <c r="J2" t="str">
+        <v>1042</v>
+      </c>
+      <c r="K2" t="str">
         <v>Recebido</v>
+      </c>
+      <c r="L2" t="str">
+        <v>NF-e 4521 emitida</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Venda de Equipamento</v>
+        <v>Venda de Equipamentos e Acessórios</v>
       </c>
       <c r="B3" t="str">
         <v>Venda de Produtos</v>
       </c>
-      <c r="C3">
-        <v>850.5</v>
+      <c r="C3" t="str">
+        <v>850,50</v>
       </c>
       <c r="D3" t="str">
         <v>25/10/2026</v>
@@ -485,27 +507,36 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>Boleto</v>
+        <v>Boleto Bancário</v>
       </c>
       <c r="G3" t="str">
         <v>Conta Bancária</v>
       </c>
       <c r="H3" t="str">
+        <v>Condomínio Parque das Flores</v>
+      </c>
+      <c r="I3" t="str">
+        <v>98.765.432/0001-10</v>
+      </c>
+      <c r="J3" t="str">
         <v/>
       </c>
-      <c r="I3" t="str">
+      <c r="K3" t="str">
         <v>Pendente</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Boleto enviado por e-mail</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Manutenção Preventiva</v>
+        <v>Manutenção Preventiva de Sistema</v>
       </c>
       <c r="B4" t="str">
         <v>Prestação de Serviços</v>
       </c>
-      <c r="C4">
-        <v>420</v>
+      <c r="C4" t="str">
+        <v>420,00</v>
       </c>
       <c r="D4" t="str">
         <v>15/10/2026</v>
@@ -523,12 +554,336 @@
         <v>João da Silva</v>
       </c>
       <c r="I4" t="str">
+        <v>123.456.789-00</v>
+      </c>
+      <c r="J4" t="str">
+        <v>1038</v>
+      </c>
+      <c r="K4" t="str">
         <v>Recebido</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Pagamento aprovado na maquininha</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Contrato Mensal de Monitoramento</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Contratos Recorrentes</v>
+      </c>
+      <c r="C5" t="str">
+        <v>650,00</v>
+      </c>
+      <c r="D5" t="str">
+        <v>10/11/2026</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v>Pix</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Conta Bancária</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Supermercado Central</v>
+      </c>
+      <c r="I5" t="str">
+        <v>22.333.444/0001-55</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Mensalidade referente ao mês corrente</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Instalação e Configuração de Câmeras</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Prestação de Serviços</v>
+      </c>
+      <c r="C6" t="str">
+        <v>1200,00</v>
+      </c>
+      <c r="D6" t="str">
+        <v>05/10/2026</v>
+      </c>
+      <c r="E6" t="str">
+        <v>05/10/2026</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Transferência</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Conta Bancária</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Clínica Bem Estar</v>
+      </c>
+      <c r="I6" t="str">
+        <v>33.444.555/0001-66</v>
+      </c>
+      <c r="J6" t="str">
+        <v>1029</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Recebido</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Serviço concluído e homologado pelo cliente</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E13"/>
+  <cols>
+    <col min="1" max="1" width="25.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="28.83203125" customWidth="1"/>
+    <col min="5" max="5" width="65.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Campo / Coluna</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Obrigatório?</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Tipo de Dado</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Exemplo</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Regras e Recomendações do Sistema</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Descrição</v>
+      </c>
+      <c r="B2" t="str">
+        <v>SIM</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Texto</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Consultoria Técnica</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Nome do serviço, produto ou título a receber.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Categoria</v>
+      </c>
+      <c r="B3" t="str">
+        <v>NÃO</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Texto</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Prestação de Serviços</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Categoria da receita. Se não existir no sistema, será cadastrada automaticamente.</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Valor (R$)</v>
+      </c>
+      <c r="B4" t="str">
+        <v>SIM</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Numérico / Moeda</v>
+      </c>
+      <c r="D4" t="str">
+        <v>1500,00 ou 1500</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Valor em Reais. Aceita vírgula ou ponto (ex: 1500,50 ou 1500.50).</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Vencimento</v>
+      </c>
+      <c r="B5" t="str">
+        <v>SIM</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Data (DD/MM/AAAA)</v>
+      </c>
+      <c r="D5" t="str">
+        <v>20/10/2026</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Data limite de vencimento do título.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Data de Pagamento</v>
+      </c>
+      <c r="B6" t="str">
+        <v>NÃO</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Data (DD/MM/AAAA)</v>
+      </c>
+      <c r="D6" t="str">
+        <v>20/10/2026</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Data em que o cliente pagou. Se deixada em branco, o sistema assume automaticamente a mesma data de vencimento.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Forma de Pagamento</v>
+      </c>
+      <c r="B7" t="str">
+        <v>NÃO</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Texto</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Pix, Boleto, Cartão</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Forma de pagamento utilizada (Pix, Boleto Bancário, Cartão de Crédito, Transferência, Dinheiro, etc.).</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Caixa / Origem</v>
+      </c>
+      <c r="B8" t="str">
+        <v>NÃO</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Texto</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Caixa Principal</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Conta bancária ou caixa onde o valor foi ou será depositado.</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Cliente</v>
+      </c>
+      <c r="B9" t="str">
+        <v>NÃO</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Texto</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Empresa Exemplo LTDA</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Nome ou Razão Social do cliente. Se ainda não existir no cadastro, será criado automaticamente.</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>CPF / CNPJ</v>
+      </c>
+      <c r="B10" t="str">
+        <v>NÃO</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Texto / Documento</v>
+      </c>
+      <c r="D10" t="str">
+        <v>12.345.678/0001-90</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Documento do cliente para identificação ou novo cadastro unívoco.</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Ordem de Serviço (O.S.)</v>
+      </c>
+      <c r="B11" t="str">
+        <v>NÃO</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Número</v>
+      </c>
+      <c r="D11" t="str">
+        <v>1042</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Número da O.S. ou Ocorrência vinculada (se aplicável).</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Status</v>
+      </c>
+      <c r="B12" t="str">
+        <v>NÃO</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Texto</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Recebido ou Pendente</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Status atual da conta. Se não informado, o padrão é "Pendente" (ou "Recebido" se a data for informada/passada).</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Observações</v>
+      </c>
+      <c r="B13" t="str">
+        <v>NÃO</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Texto</v>
+      </c>
+      <c r="D13" t="str">
+        <v>NF-e 4521 emitida</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Campo livre para anotações, detalhes adicionais ou números de notas fiscais.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E13"/>
   </ignoredErrors>
 </worksheet>
 </file>